--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$34</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1056,6 +1059,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1380,7 +1398,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
@@ -1488,7 +1506,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>81</v>
       </c>
@@ -1596,7 +1614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>89</v>
       </c>
@@ -1702,7 +1720,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>95</v>
       </c>
@@ -1810,7 +1828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>101</v>
       </c>
@@ -1918,7 +1936,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>110</v>
       </c>
@@ -2026,7 +2044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>118</v>
       </c>
@@ -2134,7 +2152,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>126</v>
       </c>
@@ -2242,7 +2260,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>134</v>
       </c>
@@ -2352,7 +2370,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>139</v>
       </c>
@@ -2460,7 +2478,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>147</v>
       </c>
@@ -2568,7 +2586,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -2676,7 +2694,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>162</v>
       </c>
@@ -2786,7 +2804,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>171</v>
       </c>
@@ -2906,13 +2924,13 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>75</v>
@@ -3006,7 +3024,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>192</v>
       </c>
@@ -3116,7 +3134,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>201</v>
       </c>
@@ -3226,7 +3244,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>211</v>
       </c>
@@ -3336,7 +3354,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>221</v>
       </c>
@@ -3446,7 +3464,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>229</v>
       </c>
@@ -3554,7 +3572,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>236</v>
       </c>
@@ -3660,7 +3678,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>242</v>
       </c>
@@ -3768,7 +3786,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>245</v>
       </c>
@@ -3878,7 +3896,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>250</v>
       </c>
@@ -3986,7 +4004,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>256</v>
       </c>
@@ -4096,7 +4114,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>262</v>
       </c>
@@ -4204,7 +4222,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>267</v>
       </c>
@@ -4312,7 +4330,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>272</v>
       </c>
@@ -4418,7 +4436,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>273</v>
       </c>
@@ -4526,7 +4544,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>274</v>
       </c>
@@ -4636,7 +4654,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>275</v>
       </c>
@@ -4746,7 +4764,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>285</v>
       </c>
@@ -4854,7 +4872,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>289</v>
       </c>
@@ -4963,6 +4981,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL34">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI33">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
 Focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
 Focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -619,7 +619,7 @@
     <t>QuestionnaireResponse.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/EncounterAtenderLE)
 </t>
   </si>
   <si>
@@ -2914,7 +2914,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>182</v>
       </c>
@@ -2924,13 +2924,13 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>75</v>
@@ -3024,7 +3024,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>192</v>
       </c>
@@ -3034,13 +3034,13 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
+++ b/refs/heads/master/StructureDefinition-QuestionnaireResponseAtenderLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
